--- a/data/trans_dic/P62A$jubilacion-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P62A$jubilacion-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de jubilación</t>
+          <t>Población que, al menos, percibe una pensión de jubilación (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,57; 93,66</t>
+          <t>84,32; 93,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,12; 83,34</t>
+          <t>71,03; 83,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,6; 91,02</t>
+          <t>80,28; 91,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,67; 61,26</t>
+          <t>48,63; 60,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,61; 57,07</t>
+          <t>39,97; 57,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,09; 50,09</t>
+          <t>35,81; 51,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,19; 55,99</t>
+          <t>38,77; 54,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,84; 33,77</t>
+          <t>24,45; 33,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,78; 77,26</t>
+          <t>66,76; 76,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57,52; 67,53</t>
+          <t>57,15; 67,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63,24; 73,85</t>
+          <t>63,45; 73,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,3; 46,37</t>
+          <t>38,35; 46,58</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,74; 93,61</t>
+          <t>85,37; 93,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,11; 78,41</t>
+          <t>66,62; 78,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75,65; 85,22</t>
+          <t>75,29; 85,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,07; 58,87</t>
+          <t>46,56; 58,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,72; 36,38</t>
+          <t>21,39; 36,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,06; 43,22</t>
+          <t>28,74; 43,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,77; 53,77</t>
+          <t>39,1; 54,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,86; 33,03</t>
+          <t>23,84; 33,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59,19; 69,38</t>
+          <t>59,57; 69,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,03; 61,04</t>
+          <t>51,01; 61,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61,09; 70,24</t>
+          <t>61,15; 69,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,28; 45,31</t>
+          <t>37,33; 45,13</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,52; 90,97</t>
+          <t>79,78; 90,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,45; 80,34</t>
+          <t>64,76; 79,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,81; 90,24</t>
+          <t>78,7; 90,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45,16; 58,7</t>
+          <t>45,34; 58,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,66; 45,88</t>
+          <t>28,14; 46,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,35; 36,07</t>
+          <t>20,01; 35,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,37; 51,86</t>
+          <t>33,87; 51,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,55; 93,33</t>
+          <t>26,9; 91,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58,52; 70,37</t>
+          <t>58,63; 70,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,83; 57,68</t>
+          <t>45,69; 57,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61,76; 72,9</t>
+          <t>61,32; 72,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,92; 84,91</t>
+          <t>40,38; 85,26</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,95; 93,99</t>
+          <t>85,09; 93,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,95; 85,6</t>
+          <t>74,86; 85,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,49; 87,18</t>
+          <t>77,65; 87,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,79; 54,94</t>
+          <t>44,18; 55,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,18; 50,43</t>
+          <t>35,98; 51,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,25; 42,38</t>
+          <t>28,95; 42,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,32; 45,96</t>
+          <t>31,88; 45,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,0; 42,34</t>
+          <t>33,38; 42,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,67; 72,21</t>
+          <t>62,22; 72,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53,96; 63,57</t>
+          <t>54,41; 63,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,09; 66,1</t>
+          <t>57,19; 66,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40,02; 47,14</t>
+          <t>40,14; 47,59</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,54; 91,23</t>
+          <t>86,53; 91,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,16; 79,17</t>
+          <t>73,13; 79,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,8; 86,13</t>
+          <t>80,6; 85,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49,18; 55,22</t>
+          <t>49,34; 55,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,09; 43,06</t>
+          <t>34,92; 42,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,81; 39,39</t>
+          <t>32,15; 39,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,38; 47,21</t>
+          <t>39,12; 47,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,59; 72,56</t>
+          <t>30,52; 71,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64,44; 69,68</t>
+          <t>64,47; 69,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55,07; 60,04</t>
+          <t>54,9; 60,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63,01; 67,74</t>
+          <t>62,79; 67,48</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,78; 65,94</t>
+          <t>41,72; 66,3</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de jubilación</t>
+          <t>Población que, al menos, percibe una pensión de jubilación (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>144708; 160259</t>
+          <t>144278; 160183</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>150393; 176241</t>
+          <t>150208; 175926</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>152724; 172485</t>
+          <t>152121; 173022</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87589; 110240</t>
+          <t>87514; 109674</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50166; 72279</t>
+          <t>50621; 72378</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57549; 82161</t>
+          <t>58733; 84160</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56943; 83494</t>
+          <t>57819; 81857</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42249; 57444</t>
+          <t>41586; 56869</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>198836; 230052</t>
+          <t>198782; 228727</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>215978; 253551</t>
+          <t>214573; 253529</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>214155; 250072</t>
+          <t>214846; 250525</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>134082; 162310</t>
+          <t>134244; 163041</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>190800; 208293</t>
+          <t>189956; 207753</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>165245; 193088</t>
+          <t>164043; 193608</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>200191; 225506</t>
+          <t>199228; 225333</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93278; 116661</t>
+          <t>92261; 116803</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33320; 55806</t>
+          <t>32813; 55240</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60961; 90650</t>
+          <t>60276; 90407</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79026; 109623</t>
+          <t>79711; 110125</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44005; 60930</t>
+          <t>43982; 60986</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>222517; 260789</t>
+          <t>223928; 261818</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>232695; 278343</t>
+          <t>232586; 278421</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>286182; 329042</t>
+          <t>286482; 327776</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>142650; 173386</t>
+          <t>142837; 172698</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>122762; 140442</t>
+          <t>123173; 140020</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>110446; 135567</t>
+          <t>109273; 134637</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>143498; 164309</t>
+          <t>143283; 164729</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90715; 117907</t>
+          <t>91069; 117101</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33144; 54965</t>
+          <t>33712; 55356</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30090; 53334</t>
+          <t>29592; 52932</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45197; 70242</t>
+          <t>45882; 70412</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>95744; 324343</t>
+          <t>93494; 317918</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>160450; 192944</t>
+          <t>160751; 192817</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145095; 182608</t>
+          <t>144656; 182883</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>196093; 231460</t>
+          <t>194718; 231157</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>218900; 465652</t>
+          <t>221437; 467555</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>161292; 178455</t>
+          <t>161544; 178158</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>183391; 209433</t>
+          <t>183159; 209736</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>205378; 231069</t>
+          <t>205818; 231741</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>97416; 122226</t>
+          <t>98296; 123326</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>62000; 88881</t>
+          <t>63419; 90344</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65651; 95124</t>
+          <t>64982; 95516</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>80363; 114273</t>
+          <t>79261; 113456</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>77710; 99721</t>
+          <t>78605; 100487</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>229440; 264376</t>
+          <t>227777; 265660</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>253112; 298223</t>
+          <t>255259; 298299</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>293237; 339518</t>
+          <t>293769; 339737</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>183291; 215909</t>
+          <t>183825; 217939</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>638560; 673151</t>
+          <t>638499; 672924</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>637330; 689653</t>
+          <t>637078; 692109</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>728215; 776258</t>
+          <t>726361; 774060</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>394198; 442602</t>
+          <t>395485; 444252</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>202158; 248046</t>
+          <t>201156; 247086</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>237356; 293882</t>
+          <t>239895; 295315</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>290214; 347978</t>
+          <t>288316; 346981</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>286820; 680323</t>
+          <t>286160; 674187</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>846704; 915506</t>
+          <t>847160; 914828</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>890632; 970909</t>
+          <t>887821; 971263</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1032356; 1109783</t>
+          <t>1028731; 1105522</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>726665; 1146732</t>
+          <t>725456; 1152980</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$jubilacion-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P62A$jubilacion-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,59%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,32; 93,61</t>
+          <t>83,48; 93,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,03; 83,2</t>
+          <t>71,14; 83,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,28; 91,31</t>
+          <t>80,59; 90,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,63; 60,94</t>
+          <t>48,23; 61,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,97; 57,15</t>
+          <t>40,1; 56,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,81; 51,31</t>
+          <t>34,09; 50,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,77; 54,89</t>
+          <t>38,34; 55,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,45; 33,44</t>
+          <t>24,68; 33,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,76; 76,82</t>
+          <t>66,73; 77,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57,15; 67,52</t>
+          <t>57,44; 67,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63,45; 73,99</t>
+          <t>63,72; 73,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,35; 46,58</t>
+          <t>38,64; 46,54</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,34%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>85,37; 93,36</t>
+          <t>84,79; 93,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>66,62; 78,62</t>
+          <t>67,0; 78,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75,29; 85,16</t>
+          <t>75,42; 85,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46,56; 58,94</t>
+          <t>46,82; 58,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,39; 36,01</t>
+          <t>20,79; 35,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,74; 43,1</t>
+          <t>29,58; 43,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,1; 54,02</t>
+          <t>39,27; 53,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,84; 33,06</t>
+          <t>24,65; 33,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59,57; 69,65</t>
+          <t>59,27; 69,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,01; 61,06</t>
+          <t>51,17; 60,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61,15; 69,97</t>
+          <t>61,26; 70,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,33; 45,13</t>
+          <t>37,61; 45,28</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>79,78; 90,7</t>
+          <t>80,16; 91,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,76; 79,79</t>
+          <t>65,24; 79,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78,7; 90,48</t>
+          <t>78,79; 90,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45,34; 58,3</t>
+          <t>46,35; 59,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,14; 46,2</t>
+          <t>29,17; 47,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,01; 35,8</t>
+          <t>20,03; 35,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,87; 51,98</t>
+          <t>33,75; 52,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,9; 91,48</t>
+          <t>24,18; 35,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58,63; 70,32</t>
+          <t>58,44; 70,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,69; 57,76</t>
+          <t>45,57; 58,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61,32; 72,8</t>
+          <t>61,36; 72,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,38; 85,26</t>
+          <t>38,28; 47,73</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,09; 93,84</t>
+          <t>85,13; 94,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,86; 85,72</t>
+          <t>74,75; 86,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,65; 87,43</t>
+          <t>77,61; 87,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,18; 55,44</t>
+          <t>43,71; 55,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,98; 51,26</t>
+          <t>35,82; 50,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,95; 42,56</t>
+          <t>29,03; 43,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,88; 45,64</t>
+          <t>32,64; 46,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,38; 42,67</t>
+          <t>33,16; 43,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,22; 72,56</t>
+          <t>62,7; 72,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54,41; 63,59</t>
+          <t>54,47; 63,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,19; 66,14</t>
+          <t>56,85; 66,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40,14; 47,59</t>
+          <t>39,57; 46,58</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,53; 91,2</t>
+          <t>86,66; 91,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,13; 79,45</t>
+          <t>73,21; 79,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,6; 85,89</t>
+          <t>81,03; 86,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49,34; 55,43</t>
+          <t>49,2; 55,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,92; 42,89</t>
+          <t>35,11; 43,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,15; 39,58</t>
+          <t>32,34; 39,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,12; 47,08</t>
+          <t>39,17; 47,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,52; 71,91</t>
+          <t>29,69; 34,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64,47; 69,62</t>
+          <t>64,7; 69,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54,9; 60,06</t>
+          <t>54,96; 60,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62,79; 67,48</t>
+          <t>63,1; 67,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>41,72; 66,3</t>
+          <t>40,72; 44,61</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98386</t>
+          <t>108013</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49228</t>
+          <t>52961</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>147614</t>
+          <t>160974</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>144278; 160183</t>
+          <t>142848; 160211</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>150208; 175926</t>
+          <t>150440; 176184</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>152121; 173022</t>
+          <t>152707; 172314</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87514; 109674</t>
+          <t>94838; 119985</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>50621; 72378</t>
+          <t>50785; 71979</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58733; 84160</t>
+          <t>55910; 82144</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57819; 81857</t>
+          <t>57175; 82600</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41586; 56869</t>
+          <t>44752; 61598</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>198782; 228727</t>
+          <t>198687; 229420</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>214573; 253529</t>
+          <t>215696; 253542</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>214846; 250525</t>
+          <t>215757; 249586</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>134244; 163041</t>
+          <t>146025; 175866</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105408</t>
+          <t>116269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52113</t>
+          <t>58586</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>157521</t>
+          <t>174856</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>189956; 207753</t>
+          <t>188683; 207815</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>164043; 193608</t>
+          <t>164973; 194078</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>199228; 225333</t>
+          <t>199572; 225766</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92261; 116803</t>
+          <t>102784; 129306</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32813; 55240</t>
+          <t>31892; 54467</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60276; 90407</t>
+          <t>62035; 90821</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79711; 110125</t>
+          <t>80053; 109440</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43982; 60986</t>
+          <t>50145; 68954</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>223928; 261818</t>
+          <t>222785; 260571</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>232586; 278421</t>
+          <t>233309; 275165</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>286482; 327776</t>
+          <t>287000; 330584</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>142837; 172698</t>
+          <t>159084; 191522</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103551</t>
+          <t>119295</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>246067</t>
+          <t>48504</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>349618</t>
+          <t>167799</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>123173; 140020</t>
+          <t>123748; 140956</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>109273; 134637</t>
+          <t>110084; 134877</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>143283; 164729</t>
+          <t>143455; 164544</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91069; 117101</t>
+          <t>104952; 133695</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33712; 55356</t>
+          <t>34947; 56736</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29592; 52932</t>
+          <t>29618; 52112</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45882; 70412</t>
+          <t>45717; 70805</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>93494; 317918</t>
+          <t>39263; 57841</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>160751; 192817</t>
+          <t>160234; 192133</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144656; 182883</t>
+          <t>144271; 183990</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>194718; 231157</t>
+          <t>194831; 230902</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>221437; 467555</t>
+          <t>148838; 185574</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111034</t>
+          <t>114121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>88676</t>
+          <t>97568</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>199710</t>
+          <t>211690</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>161544; 178158</t>
+          <t>161619; 179069</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>183159; 209736</t>
+          <t>182888; 210608</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>205818; 231741</t>
+          <t>205707; 230910</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>98296; 123326</t>
+          <t>101336; 127922</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63419; 90344</t>
+          <t>63127; 89115</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64982; 95516</t>
+          <t>65145; 96531</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79261; 113456</t>
+          <t>81147; 115259</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>78605; 100487</t>
+          <t>85143; 110637</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>227777; 265660</t>
+          <t>229548; 264303</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>255259; 298299</t>
+          <t>255527; 298024</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>293769; 339737</t>
+          <t>292014; 339528</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>183825; 217939</t>
+          <t>193329; 227573</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418379</t>
+          <t>457699</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>436084</t>
+          <t>257619</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>854463</t>
+          <t>715317</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>638499; 672924</t>
+          <t>639437; 672786</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>637078; 692109</t>
+          <t>637702; 690614</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>726361; 774060</t>
+          <t>730260; 775679</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>395485; 444252</t>
+          <t>430253; 485431</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>201156; 247086</t>
+          <t>202254; 249874</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>239895; 295315</t>
+          <t>241307; 294932</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>288316; 346981</t>
+          <t>288692; 346949</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>286160; 674187</t>
+          <t>238666; 279168</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>847160; 914828</t>
+          <t>850179; 919693</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>887821; 971263</t>
+          <t>888787; 971285</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1028731; 1105522</t>
+          <t>1033720; 1108884</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>725456; 1152980</t>
+          <t>683385; 748748</t>
         </is>
       </c>
     </row>
